--- a/DateBase/orders/Dang Nguyen48_2026-6-26.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-6-26.xlsx
@@ -1071,6 +1071,9 @@
       <c r="G2" t="str">
         <v>01051515105101052010151510105555514101085119851010513145610105351052051010201051055101010101030355585100</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
